--- a/docs/verification/files/rocscience/joints/rj017_staircase.xlsx
+++ b/docs/verification/files/rocscience/joints/rj017_staircase.xlsx
@@ -13737,20 +13737,10 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>21.95</v>
-      </c>
-      <c r="C3" s="3">
-        <v>31.8</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E3" s="3">
-        <v>7.6864664555</v>
-      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
